--- a/tool/track-aggregator/clients/template/client.xlsx
+++ b/tool/track-aggregator/clients/template/client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D7A27-C223-4761-913F-234DFEA9F362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC3FB90-A473-4234-983A-DB6E3B3A8793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -758,19 +758,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="44" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="44" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
@@ -779,8 +770,17 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="45">
@@ -1147,887 +1147,887 @@
     <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.19921875" customWidth="1"/>
-    <col min="6" max="6" width="20.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="6"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F3" s="6"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F4" s="6"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F5" s="6"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F6" s="6"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F7" s="6"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F8" s="6"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F9" s="6"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F10" s="6"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F11" s="6"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F12" s="6"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F13" s="6"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F14" s="6"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F15" s="6"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F16" s="6"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F17" s="6"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F18" s="6"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F19" s="6"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F20" s="6"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F21" s="6"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F22" s="6"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F23" s="6"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F24" s="6"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F25" s="6"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F26" s="6"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F27" s="6"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F28" s="6"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F29" s="6"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F30" s="6"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F31" s="6"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F32" s="6"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F33" s="6"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F34" s="6"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F35" s="6"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F36" s="6"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F37" s="6"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F38" s="6"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F39" s="6"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F40" s="6"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F41" s="6"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F42" s="6"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F43" s="6"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F44" s="6"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F45" s="6"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F46" s="6"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F47" s="6"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F48" s="6"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F49" s="6"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F50" s="6"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F51" s="6"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F52" s="6"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F53" s="6"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F54" s="6"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F55" s="6"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F56" s="6"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F57" s="6"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F58" s="6"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F59" s="6"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F60" s="6"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F61" s="6"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F62" s="6"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F63" s="6"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F64" s="6"/>
+      <c r="F64" s="3"/>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F65" s="6"/>
+      <c r="F65" s="3"/>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F66" s="6"/>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F67" s="6"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F68" s="6"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F69" s="6"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F70" s="6"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F71" s="6"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F72" s="6"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F73" s="6"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F74" s="6"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F75" s="6"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F76" s="6"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F77" s="6"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F78" s="6"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F79" s="6"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F80" s="6"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F81" s="6"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F82" s="6"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F83" s="6"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F84" s="6"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F85" s="6"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F86" s="6"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F87" s="6"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F88" s="6"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F89" s="6"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F90" s="6"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F91" s="6"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F92" s="6"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F93" s="6"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F94" s="6"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F95" s="6"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F96" s="6"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F97" s="6"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F98" s="6"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F99" s="6"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F100" s="6"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F101" s="6"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F102" s="6"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F103" s="6"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F104" s="6"/>
+      <c r="F104" s="3"/>
     </row>
     <row r="105" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F105" s="6"/>
+      <c r="F105" s="3"/>
     </row>
     <row r="106" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F106" s="6"/>
+      <c r="F106" s="3"/>
     </row>
     <row r="107" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F107" s="6"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F108" s="6"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F109" s="6"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F110" s="6"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F111" s="6"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F112" s="6"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F113" s="6"/>
+      <c r="F113" s="3"/>
     </row>
     <row r="114" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F114" s="6"/>
+      <c r="F114" s="3"/>
     </row>
     <row r="115" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F115" s="6"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F116" s="6"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F117" s="6"/>
+      <c r="F117" s="3"/>
     </row>
     <row r="118" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F118" s="6"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F119" s="6"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F120" s="6"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F121" s="6"/>
+      <c r="F121" s="3"/>
     </row>
     <row r="122" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F122" s="6"/>
+      <c r="F122" s="3"/>
     </row>
     <row r="123" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F123" s="6"/>
+      <c r="F123" s="3"/>
     </row>
     <row r="124" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F124" s="6"/>
+      <c r="F124" s="3"/>
     </row>
     <row r="125" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F125" s="6"/>
+      <c r="F125" s="3"/>
     </row>
     <row r="126" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F126" s="6"/>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F127" s="6"/>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F128" s="6"/>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F129" s="6"/>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F130" s="6"/>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F131" s="6"/>
+      <c r="F131" s="3"/>
     </row>
     <row r="132" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F132" s="6"/>
+      <c r="F132" s="3"/>
     </row>
     <row r="133" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F133" s="6"/>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F134" s="6"/>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F135" s="6"/>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F136" s="6"/>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F137" s="6"/>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F138" s="6"/>
+      <c r="F138" s="3"/>
     </row>
     <row r="139" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F139" s="6"/>
+      <c r="F139" s="3"/>
     </row>
     <row r="140" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F140" s="6"/>
+      <c r="F140" s="3"/>
     </row>
     <row r="141" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F141" s="6"/>
+      <c r="F141" s="3"/>
     </row>
     <row r="142" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F142" s="6"/>
+      <c r="F142" s="3"/>
     </row>
     <row r="143" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F143" s="6"/>
+      <c r="F143" s="3"/>
     </row>
     <row r="144" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F144" s="6"/>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F145" s="6"/>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F146" s="7"/>
+      <c r="F146" s="4"/>
     </row>
     <row r="147" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F147" s="6"/>
+      <c r="F147" s="3"/>
     </row>
     <row r="148" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F148" s="6"/>
+      <c r="F148" s="3"/>
     </row>
     <row r="149" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F149" s="6"/>
+      <c r="F149" s="3"/>
     </row>
     <row r="150" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F150" s="6"/>
+      <c r="F150" s="3"/>
     </row>
     <row r="151" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F151" s="6"/>
+      <c r="F151" s="3"/>
     </row>
     <row r="152" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F152" s="6"/>
+      <c r="F152" s="3"/>
     </row>
     <row r="153" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F153" s="6"/>
+      <c r="F153" s="3"/>
     </row>
     <row r="154" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F154" s="6"/>
+      <c r="F154" s="3"/>
     </row>
     <row r="155" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F155" s="6"/>
+      <c r="F155" s="3"/>
     </row>
     <row r="156" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F156" s="6"/>
+      <c r="F156" s="3"/>
     </row>
     <row r="157" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F157" s="6"/>
+      <c r="F157" s="3"/>
     </row>
     <row r="158" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F158" s="6"/>
+      <c r="F158" s="3"/>
     </row>
     <row r="159" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F159" s="6"/>
+      <c r="F159" s="3"/>
     </row>
     <row r="160" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F160" s="6"/>
+      <c r="F160" s="3"/>
     </row>
     <row r="161" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F161" s="6"/>
+      <c r="F161" s="3"/>
     </row>
     <row r="162" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F162" s="6"/>
+      <c r="F162" s="3"/>
     </row>
     <row r="163" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F163" s="6"/>
+      <c r="F163" s="3"/>
     </row>
     <row r="164" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F164" s="6"/>
+      <c r="F164" s="3"/>
     </row>
     <row r="165" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F165" s="6"/>
+      <c r="F165" s="3"/>
     </row>
     <row r="166" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F166" s="6"/>
+      <c r="F166" s="3"/>
     </row>
     <row r="167" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F167" s="6"/>
+      <c r="F167" s="3"/>
     </row>
     <row r="168" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F168" s="6"/>
+      <c r="F168" s="3"/>
     </row>
     <row r="169" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F169" s="6"/>
+      <c r="F169" s="3"/>
     </row>
     <row r="170" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F170" s="6"/>
+      <c r="F170" s="3"/>
     </row>
     <row r="171" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F171" s="6"/>
+      <c r="F171" s="3"/>
     </row>
     <row r="172" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F172" s="6"/>
+      <c r="F172" s="3"/>
     </row>
     <row r="173" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F173" s="6"/>
+      <c r="F173" s="3"/>
     </row>
     <row r="174" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F174" s="6"/>
+      <c r="F174" s="3"/>
     </row>
     <row r="175" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F175" s="6"/>
+      <c r="F175" s="3"/>
     </row>
     <row r="176" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F176" s="6"/>
+      <c r="F176" s="3"/>
     </row>
     <row r="177" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F177" s="6"/>
+      <c r="F177" s="3"/>
     </row>
     <row r="178" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F178" s="6"/>
+      <c r="F178" s="3"/>
     </row>
     <row r="179" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F179" s="6"/>
+      <c r="F179" s="3"/>
     </row>
     <row r="180" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F180" s="6"/>
+      <c r="F180" s="3"/>
     </row>
     <row r="181" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F181" s="6"/>
+      <c r="F181" s="3"/>
     </row>
     <row r="182" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F182" s="6"/>
+      <c r="F182" s="3"/>
     </row>
     <row r="183" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F183" s="6"/>
+      <c r="F183" s="3"/>
     </row>
     <row r="184" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F184" s="6"/>
+      <c r="F184" s="3"/>
     </row>
     <row r="185" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F185" s="6"/>
+      <c r="F185" s="3"/>
     </row>
     <row r="186" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F186" s="6"/>
+      <c r="F186" s="3"/>
     </row>
     <row r="187" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F187" s="6"/>
+      <c r="F187" s="3"/>
     </row>
     <row r="188" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F188" s="6"/>
+      <c r="F188" s="3"/>
     </row>
     <row r="189" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F189" s="6"/>
+      <c r="F189" s="3"/>
     </row>
     <row r="190" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F190" s="6"/>
+      <c r="F190" s="3"/>
     </row>
     <row r="191" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F191" s="6"/>
+      <c r="F191" s="3"/>
     </row>
     <row r="192" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F192" s="6"/>
+      <c r="F192" s="3"/>
     </row>
     <row r="193" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F193" s="6"/>
+      <c r="F193" s="3"/>
     </row>
     <row r="194" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F194" s="6"/>
+      <c r="F194" s="3"/>
     </row>
     <row r="195" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F195" s="6"/>
+      <c r="F195" s="3"/>
     </row>
     <row r="196" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F196" s="6"/>
+      <c r="F196" s="3"/>
     </row>
     <row r="197" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F197" s="6"/>
+      <c r="F197" s="3"/>
     </row>
     <row r="198" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F198" s="6"/>
+      <c r="F198" s="3"/>
     </row>
     <row r="199" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F199" s="6"/>
+      <c r="F199" s="3"/>
     </row>
     <row r="200" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F200" s="6"/>
+      <c r="F200" s="3"/>
     </row>
     <row r="201" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F201" s="6"/>
+      <c r="F201" s="3"/>
     </row>
     <row r="202" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F202" s="6"/>
+      <c r="F202" s="3"/>
     </row>
     <row r="203" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F203" s="6"/>
+      <c r="F203" s="3"/>
     </row>
     <row r="204" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F204" s="6"/>
+      <c r="F204" s="3"/>
     </row>
     <row r="205" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F205" s="6"/>
+      <c r="F205" s="3"/>
     </row>
     <row r="206" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F206" s="6"/>
+      <c r="F206" s="3"/>
     </row>
     <row r="207" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F207" s="6"/>
+      <c r="F207" s="3"/>
     </row>
     <row r="208" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F208" s="6"/>
+      <c r="F208" s="3"/>
     </row>
     <row r="209" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F209" s="6"/>
+      <c r="F209" s="3"/>
     </row>
     <row r="210" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F210" s="6"/>
+      <c r="F210" s="3"/>
     </row>
     <row r="211" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F211" s="6"/>
+      <c r="F211" s="3"/>
     </row>
     <row r="212" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F212" s="6"/>
+      <c r="F212" s="3"/>
     </row>
     <row r="213" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F213" s="6"/>
+      <c r="F213" s="3"/>
     </row>
     <row r="214" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F214" s="6"/>
+      <c r="F214" s="3"/>
     </row>
     <row r="215" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F215" s="6"/>
+      <c r="F215" s="3"/>
     </row>
     <row r="216" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F216" s="6"/>
+      <c r="F216" s="3"/>
     </row>
     <row r="217" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F217" s="6"/>
+      <c r="F217" s="3"/>
     </row>
     <row r="218" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F218" s="6"/>
+      <c r="F218" s="3"/>
     </row>
     <row r="219" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F219" s="6"/>
+      <c r="F219" s="3"/>
     </row>
     <row r="220" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F220" s="6"/>
+      <c r="F220" s="3"/>
     </row>
     <row r="221" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F221" s="6"/>
+      <c r="F221" s="3"/>
     </row>
     <row r="222" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F222" s="6"/>
+      <c r="F222" s="3"/>
     </row>
     <row r="223" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F223" s="6"/>
+      <c r="F223" s="3"/>
     </row>
     <row r="224" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F224" s="6"/>
+      <c r="F224" s="3"/>
     </row>
     <row r="225" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F225" s="6"/>
+      <c r="F225" s="3"/>
     </row>
     <row r="226" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F226" s="6"/>
+      <c r="F226" s="3"/>
     </row>
     <row r="227" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F227" s="6"/>
+      <c r="F227" s="3"/>
     </row>
     <row r="228" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F228" s="6"/>
+      <c r="F228" s="3"/>
     </row>
     <row r="229" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F229" s="6"/>
+      <c r="F229" s="3"/>
     </row>
     <row r="230" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F230" s="6"/>
+      <c r="F230" s="3"/>
     </row>
     <row r="231" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F231" s="6"/>
+      <c r="F231" s="3"/>
     </row>
     <row r="232" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F232" s="6"/>
+      <c r="F232" s="3"/>
     </row>
     <row r="233" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F233" s="6"/>
+      <c r="F233" s="3"/>
     </row>
     <row r="234" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F234" s="6"/>
+      <c r="F234" s="3"/>
     </row>
     <row r="235" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F235" s="6"/>
+      <c r="F235" s="3"/>
     </row>
     <row r="236" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F236" s="6"/>
+      <c r="F236" s="3"/>
     </row>
     <row r="237" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F237" s="6"/>
+      <c r="F237" s="3"/>
     </row>
     <row r="238" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F238" s="6"/>
+      <c r="F238" s="3"/>
     </row>
     <row r="239" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F239" s="6"/>
+      <c r="F239" s="3"/>
     </row>
     <row r="240" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F240" s="6"/>
+      <c r="F240" s="3"/>
     </row>
     <row r="241" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F241" s="6"/>
+      <c r="F241" s="3"/>
     </row>
     <row r="242" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F242" s="6"/>
+      <c r="F242" s="3"/>
     </row>
     <row r="243" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F243" s="6"/>
+      <c r="F243" s="3"/>
     </row>
     <row r="244" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F244" s="6"/>
+      <c r="F244" s="3"/>
     </row>
     <row r="245" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F245" s="6"/>
+      <c r="F245" s="3"/>
     </row>
     <row r="246" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F246" s="6"/>
+      <c r="F246" s="3"/>
     </row>
     <row r="247" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F247" s="6"/>
+      <c r="F247" s="3"/>
     </row>
     <row r="248" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F248" s="6"/>
+      <c r="F248" s="3"/>
     </row>
     <row r="249" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F249" s="6"/>
+      <c r="F249" s="3"/>
     </row>
     <row r="250" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F250" s="6"/>
+      <c r="F250" s="3"/>
     </row>
     <row r="251" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F251" s="6"/>
+      <c r="F251" s="3"/>
     </row>
     <row r="252" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F252" s="6"/>
+      <c r="F252" s="3"/>
     </row>
     <row r="253" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F253" s="6"/>
+      <c r="F253" s="3"/>
     </row>
     <row r="254" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F254" s="6"/>
+      <c r="F254" s="3"/>
     </row>
     <row r="255" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F255" s="6"/>
+      <c r="F255" s="3"/>
     </row>
     <row r="256" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F256" s="6"/>
+      <c r="F256" s="3"/>
     </row>
     <row r="257" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F257" s="6"/>
+      <c r="F257" s="3"/>
     </row>
     <row r="258" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F258" s="6"/>
+      <c r="F258" s="3"/>
     </row>
     <row r="259" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F259" s="6"/>
+      <c r="F259" s="3"/>
     </row>
     <row r="260" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F260" s="6"/>
+      <c r="F260" s="3"/>
     </row>
     <row r="261" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F261" s="6"/>
+      <c r="F261" s="3"/>
     </row>
     <row r="262" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F262" s="6"/>
+      <c r="F262" s="3"/>
     </row>
     <row r="263" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F263" s="6"/>
+      <c r="F263" s="3"/>
     </row>
     <row r="264" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F264" s="6"/>
+      <c r="F264" s="3"/>
     </row>
     <row r="265" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F265" s="6"/>
+      <c r="F265" s="3"/>
     </row>
     <row r="266" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F266" s="6"/>
+      <c r="F266" s="3"/>
     </row>
     <row r="267" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F267" s="6"/>
+      <c r="F267" s="3"/>
     </row>
     <row r="268" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F268" s="6"/>
+      <c r="F268" s="3"/>
     </row>
     <row r="269" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F269" s="6"/>
+      <c r="F269" s="3"/>
     </row>
     <row r="270" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F270" s="6"/>
+      <c r="F270" s="3"/>
     </row>
     <row r="271" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F271" s="6"/>
+      <c r="F271" s="3"/>
     </row>
     <row r="272" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F272" s="6"/>
+      <c r="F272" s="3"/>
     </row>
     <row r="273" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F273" s="6"/>
+      <c r="F273" s="3"/>
     </row>
     <row r="274" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F274" s="6"/>
+      <c r="F274" s="3"/>
     </row>
     <row r="275" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F275" s="6"/>
+      <c r="F275" s="3"/>
     </row>
     <row r="276" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F276" s="6"/>
+      <c r="F276" s="3"/>
     </row>
     <row r="277" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F277" s="6"/>
+      <c r="F277" s="3"/>
     </row>
     <row r="278" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F278" s="6"/>
+      <c r="F278" s="3"/>
     </row>
     <row r="279" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F279" s="3"/>
+      <c r="F279" s="2"/>
     </row>
     <row r="280" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F280" s="3"/>
+      <c r="F280" s="2"/>
     </row>
     <row r="281" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F281" s="3"/>
+      <c r="F281" s="2"/>
     </row>
     <row r="282" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F282" s="3"/>
+      <c r="F282" s="2"/>
     </row>
     <row r="283" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F283" s="3"/>
+      <c r="F283" s="2"/>
     </row>
     <row r="284" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F284" s="3"/>
+      <c r="F284" s="2"/>
     </row>
     <row r="285" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F285" s="3"/>
+      <c r="F285" s="2"/>
     </row>
     <row r="286" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F286" s="3"/>
+      <c r="F286" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
@@ -2043,13 +2043,14 @@
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.69921875" customWidth="1"/>
+    <col min="4" max="5" width="10.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -2058,7 +2059,7 @@
       <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2075,13 +2076,14 @@
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.69921875" customWidth="1"/>
+    <col min="4" max="5" width="10.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -2090,7 +2092,7 @@
       <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
